--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Com\Desktop\개발\포크\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Com\Desktop\Project\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>Harvest</t>
   </si>
@@ -147,6 +147,37 @@
         <family val="2"/>
       </rPr>
       <t>Carrot</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dropItem_trap_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰덫</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>드랍된 곰덫</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Trap_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2DPrefab/DropItem_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trap</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -295,7 +326,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -352,6 +383,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -986,14 +1018,28 @@
       <c r="R7" s="5"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
+      <c r="A8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>41</v>
+      </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="30" t="s">
+        <v>42</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>

--- a/JsonConverter/ExcelFiles/DNFieldObject.xlsx
+++ b/JsonConverter/ExcelFiles/DNFieldObject.xlsx
@@ -19,21 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>Harvest</t>
   </si>
   <si>
-    <t>10,1000</t>
-  </si>
-  <si>
-    <t>10,100</t>
-  </si>
-  <si>
     <t>int[]</t>
-  </si>
-  <si>
-    <t>드랍된 금화</t>
   </si>
   <si>
     <t>string</t>
@@ -48,31 +39,13 @@
     <t>캐릭터 고유 ID</t>
   </si>
   <si>
-    <t>Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Item_Corn_1</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>IconPath</t>
   </si>
   <si>
-    <t>옥수수</t>
-  </si>
-  <si>
     <t>Id</t>
-  </si>
-  <si>
-    <t>harv_potate_1</t>
-  </si>
-  <si>
-    <t>Item_Potato_1</t>
-  </si>
-  <si>
-    <t>dropItem_gold_1</t>
   </si>
   <si>
     <t>FieldObjectType</t>
@@ -90,95 +63,21 @@
     <t>DropItemDataId</t>
   </si>
   <si>
-    <t>감자</t>
-  </si>
-  <si>
-    <t>금화</t>
-  </si>
-  <si>
-    <t>DropItem</t>
-  </si>
-  <si>
-    <t>harv_corn_1</t>
-  </si>
-  <si>
     <t>PrefabPath</t>
   </si>
   <si>
-    <t>필드 채집용 옥수수</t>
+    <t>Icon/Icon_GoldApple</t>
   </si>
   <si>
-    <t>필드 채집용 감자</t>
-  </si>
-  <si>
-    <t>2DPrefab/Harvest_Potato</t>
-  </si>
-  <si>
-    <t>2DPrefab/DropItem_Gold</t>
-  </si>
-  <si>
-    <t>2DPrefab/Harvest_Corn</t>
-  </si>
-  <si>
-    <t>harv_carrot_1</t>
+    <t>전설의 황금사과.먹을 시 복용자의 신체를 최상으로 되돌린다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>당근</t>
+    <t>harv_goldapple_1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>필드 채집용 당근</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Carrot_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2DPrefab/Harvest_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Carrot</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>dropItem_trap_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>곰덫</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>드랍된 곰덫</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Trap_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2DPrefab/DropItem_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trap</t>
-    </r>
+    <t>황금사과</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -813,97 +712,93 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E1" s="18"/>
       <c r="F1" s="18"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:18" s="13" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>27</v>
       </c>
       <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
-        <v>32</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="5"/>
       <c r="I4" s="16"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -916,28 +811,14 @@
       <c r="R4" s="5"/>
     </row>
     <row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>9</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -950,28 +831,14 @@
       <c r="R5" s="5"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A6" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>16</v>
-      </c>
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="26"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="28" t="s">
-        <v>30</v>
-      </c>
+      <c r="H6" s="28"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -984,28 +851,14 @@
       <c r="R6" s="5"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A7" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>36</v>
-      </c>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="26"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="29" t="s">
-        <v>37</v>
-      </c>
+      <c r="H7" s="29"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1018,28 +871,14 @@
       <c r="R7" s="5"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>41</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="30" t="s">
-        <v>42</v>
-      </c>
+      <c r="H8" s="30"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
